--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/23.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/23.xlsx
@@ -426,13 +426,13 @@
         <v>-15.29545340239012</v>
       </c>
       <c r="E2">
-        <v>-5.709728529278772</v>
+        <v>-7.444949199537899</v>
       </c>
       <c r="F2">
-        <v>-0.4409914757130207</v>
+        <v>-1.672931759891678</v>
       </c>
       <c r="G2">
-        <v>-10.96460411928191</v>
+        <v>-10.93335919048227</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.79760191317737</v>
       </c>
       <c r="E3">
-        <v>-6.423574529477889</v>
+        <v>-6.937293677856029</v>
       </c>
       <c r="F3">
-        <v>-0.4090813852228313</v>
+        <v>-1.740630436658968</v>
       </c>
       <c r="G3">
-        <v>-10.36371361953987</v>
+        <v>-10.53317051405855</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.23850435966392</v>
       </c>
       <c r="E4">
-        <v>-6.421346520266115</v>
+        <v>-8.657543213045798</v>
       </c>
       <c r="F4">
-        <v>-0.6368555129520367</v>
+        <v>-1.658212005260626</v>
       </c>
       <c r="G4">
-        <v>-9.396835689340332</v>
+        <v>-9.666280990781614</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.66563187213994</v>
       </c>
       <c r="E5">
-        <v>-7.455287705697411</v>
+        <v>-10.50632895446928</v>
       </c>
       <c r="F5">
-        <v>-0.4141904205060389</v>
+        <v>-1.799000293731362</v>
       </c>
       <c r="G5">
-        <v>-9.066502834340774</v>
+        <v>-10.26076227435962</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.06086110130652</v>
       </c>
       <c r="E6">
-        <v>-8.069702002110111</v>
+        <v>-8.967413103968658</v>
       </c>
       <c r="F6">
-        <v>0.1329316702478693</v>
+        <v>-1.667133020682296</v>
       </c>
       <c r="G6">
-        <v>-8.572506539516267</v>
+        <v>-9.084429438435928</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.43825232563916</v>
       </c>
       <c r="E7">
-        <v>-9.981170880747769</v>
+        <v>-10.04888515258446</v>
       </c>
       <c r="F7">
-        <v>0.08849684152542694</v>
+        <v>-1.49160455925048</v>
       </c>
       <c r="G7">
-        <v>-9.152841862004966</v>
+        <v>-9.385126289767928</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.79549776009745</v>
       </c>
       <c r="E8">
-        <v>-9.484650876650759</v>
+        <v>-11.25384868738944</v>
       </c>
       <c r="F8">
-        <v>-0.109282688018313</v>
+        <v>-1.94267013511524</v>
       </c>
       <c r="G8">
-        <v>-8.516369618806845</v>
+        <v>-8.546916022497699</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.15558480818489</v>
       </c>
       <c r="E9">
-        <v>-10.58661879862528</v>
+        <v>-12.1638455392308</v>
       </c>
       <c r="F9">
-        <v>0.07172856329275408</v>
+        <v>-1.297778751524635</v>
       </c>
       <c r="G9">
-        <v>-7.822178014131531</v>
+        <v>-7.774360494362297</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.53495535290719</v>
       </c>
       <c r="E10">
-        <v>-11.12645818507966</v>
+        <v>-13.42750262564919</v>
       </c>
       <c r="F10">
-        <v>0.1832935183588437</v>
+        <v>-1.122014317911419</v>
       </c>
       <c r="G10">
-        <v>-6.802625993856643</v>
+        <v>-6.038975833221881</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.956807181568335</v>
       </c>
       <c r="E11">
-        <v>-12.67049573968296</v>
+        <v>-15.02918765437013</v>
       </c>
       <c r="F11">
-        <v>0.270242932381258</v>
+        <v>-1.346940150551706</v>
       </c>
       <c r="G11">
-        <v>-6.544638490526779</v>
+        <v>-7.041054794140494</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.444410909276582</v>
       </c>
       <c r="E12">
-        <v>-12.94440954698492</v>
+        <v>-15.23287388676114</v>
       </c>
       <c r="F12">
-        <v>0.5227695917158242</v>
+        <v>-1.170393366216263</v>
       </c>
       <c r="G12">
-        <v>-5.825753526674041</v>
+        <v>-7.058067687666808</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.001604114724763</v>
       </c>
       <c r="E13">
-        <v>-12.75258338802</v>
+        <v>-15.45199768704429</v>
       </c>
       <c r="F13">
-        <v>0.572525672314143</v>
+        <v>-0.6380171612410115</v>
       </c>
       <c r="G13">
-        <v>-5.122941261414464</v>
+        <v>-6.285588302078809</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.637123073254825</v>
       </c>
       <c r="E14">
-        <v>-15.11204514328847</v>
+        <v>-17.94075190370576</v>
       </c>
       <c r="F14">
-        <v>0.6890753417490783</v>
+        <v>-0.3376910899666519</v>
       </c>
       <c r="G14">
-        <v>-4.843047878251243</v>
+        <v>-5.706491123621796</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.338517343866471</v>
       </c>
       <c r="E15">
-        <v>-16.00156423566715</v>
+        <v>-17.99234480807515</v>
       </c>
       <c r="F15">
-        <v>0.5832790354799768</v>
+        <v>-0.5163370764930101</v>
       </c>
       <c r="G15">
-        <v>-3.579846327377075</v>
+        <v>-5.164859389032716</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.095779393503809</v>
       </c>
       <c r="E16">
-        <v>-16.23011179036026</v>
+        <v>-17.56729318076719</v>
       </c>
       <c r="F16">
-        <v>1.205483831831911</v>
+        <v>-0.5552740701300044</v>
       </c>
       <c r="G16">
-        <v>-3.703121111622916</v>
+        <v>-5.259392016906605</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.89423086234167</v>
       </c>
       <c r="E17">
-        <v>-17.64831210923842</v>
+        <v>-19.20137491253901</v>
       </c>
       <c r="F17">
-        <v>1.062380165312803</v>
+        <v>-0.1837034045436858</v>
       </c>
       <c r="G17">
-        <v>-3.190747978509914</v>
+        <v>-4.399553955628317</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.714974546263486</v>
       </c>
       <c r="E18">
-        <v>-18.09140517699293</v>
+        <v>-20.7974219911204</v>
       </c>
       <c r="F18">
-        <v>0.9896912312059633</v>
+        <v>0.4570925155495926</v>
       </c>
       <c r="G18">
-        <v>-2.212197064738902</v>
+        <v>-3.744787637780183</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.545470564085348</v>
       </c>
       <c r="E19">
-        <v>-19.40969830231387</v>
+        <v>-20.43387156931062</v>
       </c>
       <c r="F19">
-        <v>1.331635510232156</v>
+        <v>0.2466805557713498</v>
       </c>
       <c r="G19">
-        <v>-3.158221868586575</v>
+        <v>-3.497566028544029</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.364220336577106</v>
       </c>
       <c r="E20">
-        <v>-19.37444413216415</v>
+        <v>-22.26131461273595</v>
       </c>
       <c r="F20">
-        <v>1.808218547659434</v>
+        <v>0.5518535589999118</v>
       </c>
       <c r="G20">
-        <v>-1.741434178508999</v>
+        <v>-3.948647721542964</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.15962682570782</v>
       </c>
       <c r="E21">
-        <v>-20.25026459066962</v>
+        <v>-21.69692636868599</v>
       </c>
       <c r="F21">
-        <v>1.769837434798759</v>
+        <v>1.052781323759325</v>
       </c>
       <c r="G21">
-        <v>-2.313652043335406</v>
+        <v>-3.96447212922068</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.921361748912948</v>
       </c>
       <c r="E22">
-        <v>-21.07707337499007</v>
+        <v>-24.09478052659149</v>
       </c>
       <c r="F22">
-        <v>2.206314703623447</v>
+        <v>1.36168632997762</v>
       </c>
       <c r="G22">
-        <v>-2.304968482385898</v>
+        <v>-2.852747900041405</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.64890360492494</v>
       </c>
       <c r="E23">
-        <v>-21.16679150203004</v>
+        <v>-23.73544158560884</v>
       </c>
       <c r="F23">
-        <v>2.404038803460147</v>
+        <v>0.9061602464020251</v>
       </c>
       <c r="G23">
-        <v>-1.557549926530181</v>
+        <v>-3.655859763504281</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.353321211913565</v>
       </c>
       <c r="E24">
-        <v>-21.03346869877022</v>
+        <v>-23.98453935534876</v>
       </c>
       <c r="F24">
-        <v>2.287473296966057</v>
+        <v>1.098578931422002</v>
       </c>
       <c r="G24">
-        <v>-1.284651726091439</v>
+        <v>-3.903081372740435</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.050704778896101</v>
       </c>
       <c r="E25">
-        <v>-21.60729428265217</v>
+        <v>-23.35467390562189</v>
       </c>
       <c r="F25">
-        <v>2.446390267050829</v>
+        <v>1.424823933708444</v>
       </c>
       <c r="G25">
-        <v>-2.252797595232523</v>
+        <v>-3.300826928236221</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.768150336154381</v>
       </c>
       <c r="E26">
-        <v>-21.80692753080631</v>
+        <v>-24.85145683395515</v>
       </c>
       <c r="F26">
-        <v>2.46098886817935</v>
+        <v>1.841463702236338</v>
       </c>
       <c r="G26">
-        <v>-1.52153450160845</v>
+        <v>-3.279831448426163</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.528234724811495</v>
       </c>
       <c r="E27">
-        <v>-21.9826187368819</v>
+        <v>-24.5329692569957</v>
       </c>
       <c r="F27">
-        <v>2.59415319637316</v>
+        <v>1.391605702132102</v>
       </c>
       <c r="G27">
-        <v>-2.607939678503379</v>
+        <v>-3.950809507780108</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.351866382821047</v>
       </c>
       <c r="E28">
-        <v>-21.39177514767912</v>
+        <v>-24.48739016610849</v>
       </c>
       <c r="F28">
-        <v>2.663169516462096</v>
+        <v>1.555866095975566</v>
       </c>
       <c r="G28">
-        <v>-1.946674759761656</v>
+        <v>-4.680268354085278</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.247277354584681</v>
       </c>
       <c r="E29">
-        <v>-21.7212578595292</v>
+        <v>-24.48870342357072</v>
       </c>
       <c r="F29">
-        <v>2.644027263062179</v>
+        <v>1.738693857971642</v>
       </c>
       <c r="G29">
-        <v>-2.495702253085468</v>
+        <v>-3.751196853944212</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.214514114571142</v>
       </c>
       <c r="E30">
-        <v>-21.97976126978305</v>
+        <v>-23.63657594107338</v>
       </c>
       <c r="F30">
-        <v>2.522781905587966</v>
+        <v>1.450426123537438</v>
       </c>
       <c r="G30">
-        <v>-2.288276711776893</v>
+        <v>-3.385950985687501</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.247037373726576</v>
       </c>
       <c r="E31">
-        <v>-22.47369551522169</v>
+        <v>-23.84746244713658</v>
       </c>
       <c r="F31">
-        <v>2.654687187579002</v>
+        <v>1.707931954270146</v>
       </c>
       <c r="G31">
-        <v>-2.30573321840547</v>
+        <v>-3.24641149120722</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.329607422272578</v>
       </c>
       <c r="E32">
-        <v>-21.36331821701492</v>
+        <v>-22.30834734377962</v>
       </c>
       <c r="F32">
-        <v>2.713859191697566</v>
+        <v>1.514268476400633</v>
       </c>
       <c r="G32">
-        <v>-2.622701401062989</v>
+        <v>-4.792509090048728</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.448509322672358</v>
       </c>
       <c r="E33">
-        <v>-20.92047874380484</v>
+        <v>-21.88234926540406</v>
       </c>
       <c r="F33">
-        <v>2.351217460062495</v>
+        <v>1.695919544901538</v>
       </c>
       <c r="G33">
-        <v>-2.982173677899212</v>
+        <v>-3.334558076735855</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.586984244540494</v>
       </c>
       <c r="E34">
-        <v>-21.37075849980952</v>
+        <v>-22.94034117629009</v>
       </c>
       <c r="F34">
-        <v>3.012330743344946</v>
+        <v>1.217827235736846</v>
       </c>
       <c r="G34">
-        <v>-2.396438855635961</v>
+        <v>-3.531565331232344</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.734946038164992</v>
       </c>
       <c r="E35">
-        <v>-20.48692264231047</v>
+        <v>-22.04590416113909</v>
       </c>
       <c r="F35">
-        <v>2.725546941353509</v>
+        <v>1.395360668857609</v>
       </c>
       <c r="G35">
-        <v>-2.942642453614775</v>
+        <v>-4.160072401862979</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.883755652885596</v>
       </c>
       <c r="E36">
-        <v>-20.63956844416103</v>
+        <v>-22.21122969021112</v>
       </c>
       <c r="F36">
-        <v>2.832858854183686</v>
+        <v>1.519744931456223</v>
       </c>
       <c r="G36">
-        <v>-2.899221338321694</v>
+        <v>-3.96524348633133</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.026423285826334</v>
       </c>
       <c r="E37">
-        <v>-19.12534183395022</v>
+        <v>-20.98735977642412</v>
       </c>
       <c r="F37">
-        <v>2.438444814473069</v>
+        <v>1.898326663130192</v>
       </c>
       <c r="G37">
-        <v>-2.473895689618289</v>
+        <v>-3.655522087859275</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.159826096494148</v>
       </c>
       <c r="E38">
-        <v>-19.43006737840037</v>
+        <v>-21.46741877750324</v>
       </c>
       <c r="F38">
-        <v>2.624337047415521</v>
+        <v>1.064581516535264</v>
       </c>
       <c r="G38">
-        <v>-2.580429045072036</v>
+        <v>-3.46158370907769</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.278368535714633</v>
       </c>
       <c r="E39">
-        <v>-19.05098881921828</v>
+        <v>-22.16251689531061</v>
       </c>
       <c r="F39">
-        <v>2.585859328494004</v>
+        <v>1.296797147504319</v>
       </c>
       <c r="G39">
-        <v>-2.753802314963667</v>
+        <v>-3.906001273906072</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.381103396008602</v>
       </c>
       <c r="E40">
-        <v>-17.96309992293361</v>
+        <v>-20.47775701091895</v>
       </c>
       <c r="F40">
-        <v>2.440693676872993</v>
+        <v>1.765778396537487</v>
       </c>
       <c r="G40">
-        <v>-2.652287746547456</v>
+        <v>-2.863752153413942</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.463707551910892</v>
       </c>
       <c r="E41">
-        <v>-17.58234582836868</v>
+        <v>-19.69779076173384</v>
       </c>
       <c r="F41">
-        <v>2.472275940238687</v>
+        <v>1.377349181481316</v>
       </c>
       <c r="G41">
-        <v>-2.519382585327875</v>
+        <v>-3.414974538430291</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.525751200259189</v>
       </c>
       <c r="E42">
-        <v>-16.71582685547497</v>
+        <v>-19.59822320372719</v>
       </c>
       <c r="F42">
-        <v>2.376729378654309</v>
+        <v>1.056626561722011</v>
       </c>
       <c r="G42">
-        <v>-2.294030439924146</v>
+        <v>-3.602460663955836</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.568153886460578</v>
       </c>
       <c r="E43">
-        <v>-16.25039029696661</v>
+        <v>-18.73509152939121</v>
       </c>
       <c r="F43">
-        <v>2.771304956368301</v>
+        <v>1.47205637893051</v>
       </c>
       <c r="G43">
-        <v>-1.755437786140116</v>
+        <v>-3.777283952793669</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.593700713063738</v>
       </c>
       <c r="E44">
-        <v>-15.53145429198287</v>
+        <v>-17.98103720847799</v>
       </c>
       <c r="F44">
-        <v>2.421665450298988</v>
+        <v>0.7534308153288757</v>
       </c>
       <c r="G44">
-        <v>-1.53920288315154</v>
+        <v>-4.580256773343896</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.610757598914883</v>
       </c>
       <c r="E45">
-        <v>-16.20599313779541</v>
+        <v>-17.48103933634309</v>
       </c>
       <c r="F45">
-        <v>2.444019459295416</v>
+        <v>1.074664972098867</v>
       </c>
       <c r="G45">
-        <v>-2.336561018467163</v>
+        <v>-3.184007707791958</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.625158557405944</v>
       </c>
       <c r="E46">
-        <v>-15.05079300386073</v>
+        <v>-16.47746156913323</v>
       </c>
       <c r="F46">
-        <v>2.49917360150651</v>
+        <v>1.458243295936047</v>
       </c>
       <c r="G46">
-        <v>-2.090342504529408</v>
+        <v>-3.005059479212194</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.647915628464222</v>
       </c>
       <c r="E47">
-        <v>-13.94980776074587</v>
+        <v>-15.75882444343399</v>
       </c>
       <c r="F47">
-        <v>2.739255499757553</v>
+        <v>0.8569909288453765</v>
       </c>
       <c r="G47">
-        <v>-2.197994824375428</v>
+        <v>-2.794836526922934</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.685436060329719</v>
       </c>
       <c r="E48">
-        <v>-13.06953581229086</v>
+        <v>-16.59017981565815</v>
       </c>
       <c r="F48">
-        <v>2.367646825229264</v>
+        <v>1.210827255590604</v>
       </c>
       <c r="G48">
-        <v>-1.769438083225694</v>
+        <v>-3.683347223116849</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.743391754736606</v>
       </c>
       <c r="E49">
-        <v>-12.6282450771914</v>
+        <v>-15.17460601170444</v>
       </c>
       <c r="F49">
-        <v>2.681176252720642</v>
+        <v>1.244914941714523</v>
       </c>
       <c r="G49">
-        <v>-1.743480095652269</v>
+        <v>-3.689508148365433</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.828573250398215</v>
       </c>
       <c r="E50">
-        <v>-12.85682433120257</v>
+        <v>-14.16568011669152</v>
       </c>
       <c r="F50">
-        <v>2.652553935710905</v>
+        <v>0.9777453374858035</v>
       </c>
       <c r="G50">
-        <v>-2.071121477128399</v>
+        <v>-3.388023387195084</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.942328859048092</v>
       </c>
       <c r="E51">
-        <v>-12.66344490565302</v>
+        <v>-14.40031846892495</v>
       </c>
       <c r="F51">
-        <v>2.32017048929622</v>
+        <v>0.8089903862543223</v>
       </c>
       <c r="G51">
-        <v>-1.779611389667875</v>
+        <v>-3.252277777902809</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.088506246370927</v>
       </c>
       <c r="E52">
-        <v>-11.19399584643006</v>
+        <v>-14.64651348682595</v>
       </c>
       <c r="F52">
-        <v>2.319274111748082</v>
+        <v>0.9156894048952242</v>
       </c>
       <c r="G52">
-        <v>-2.115750941543314</v>
+        <v>-4.409445865699659</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.262577608501944</v>
       </c>
       <c r="E53">
-        <v>-10.24215136628382</v>
+        <v>-13.73648493566654</v>
       </c>
       <c r="F53">
-        <v>2.796102623592252</v>
+        <v>0.759566092045288</v>
       </c>
       <c r="G53">
-        <v>-2.195975391596473</v>
+        <v>-3.464063307686605</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.463095608480545</v>
       </c>
       <c r="E54">
-        <v>-10.39284086736306</v>
+        <v>-12.90415594153074</v>
       </c>
       <c r="F54">
-        <v>2.555650138156996</v>
+        <v>0.8745668970949235</v>
       </c>
       <c r="G54">
-        <v>-2.32008443331821</v>
+        <v>-4.974827453987471</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.68564066185439</v>
       </c>
       <c r="E55">
-        <v>-9.898154895239156</v>
+        <v>-12.80310757252358</v>
       </c>
       <c r="F55">
-        <v>2.158540630978301</v>
+        <v>0.7014234967717596</v>
       </c>
       <c r="G55">
-        <v>-2.293229287903642</v>
+        <v>-3.490120611626208</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.924808726138783</v>
       </c>
       <c r="E56">
-        <v>-11.09570078961957</v>
+        <v>-12.98097697459686</v>
       </c>
       <c r="F56">
-        <v>2.220824617220704</v>
+        <v>1.075634200119116</v>
       </c>
       <c r="G56">
-        <v>-2.620238355181772</v>
+        <v>-4.330969383691236</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.177914542334502</v>
       </c>
       <c r="E57">
-        <v>-8.465540443594584</v>
+        <v>-11.13021681850603</v>
       </c>
       <c r="F57">
-        <v>2.803688574927207</v>
+        <v>0.8920383407540515</v>
       </c>
       <c r="G57">
-        <v>-2.696274965127752</v>
+        <v>-3.762333529138321</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.434415309681109</v>
       </c>
       <c r="E58">
-        <v>-8.641077681553909</v>
+        <v>-10.38018831098563</v>
       </c>
       <c r="F58">
-        <v>2.170920460119291</v>
+        <v>0.6605021196227198</v>
       </c>
       <c r="G58">
-        <v>-2.646778998770109</v>
+        <v>-4.309586570053083</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.693543142392183</v>
       </c>
       <c r="E59">
-        <v>-8.224132022719685</v>
+        <v>-10.39975584717277</v>
       </c>
       <c r="F59">
-        <v>2.500138078409013</v>
+        <v>0.6799769512648787</v>
       </c>
       <c r="G59">
-        <v>-2.843269808162471</v>
+        <v>-4.273461897128557</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.949155767039102</v>
       </c>
       <c r="E60">
-        <v>-6.972842198816242</v>
+        <v>-11.1605440089354</v>
       </c>
       <c r="F60">
-        <v>2.24749897595445</v>
+        <v>0.9508635132771344</v>
       </c>
       <c r="G60">
-        <v>-3.162972501435429</v>
+        <v>-4.649284958383239</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.199107405065106</v>
       </c>
       <c r="E61">
-        <v>-7.944045905345273</v>
+        <v>-11.83255596625166</v>
       </c>
       <c r="F61">
-        <v>2.153710327936211</v>
+        <v>0.5009690879368425</v>
       </c>
       <c r="G61">
-        <v>-3.540288618728324</v>
+        <v>-4.313519498153737</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.44330531289039</v>
       </c>
       <c r="E62">
-        <v>-7.903692673462922</v>
+        <v>-10.66534179077462</v>
       </c>
       <c r="F62">
-        <v>2.509504115192922</v>
+        <v>0.8369206237790124</v>
       </c>
       <c r="G62">
-        <v>-3.114254513279514</v>
+        <v>-4.756414212034055</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.678132592930353</v>
       </c>
       <c r="E63">
-        <v>-7.461070567005206</v>
+        <v>-10.55534515712831</v>
       </c>
       <c r="F63">
-        <v>2.591007956425097</v>
+        <v>0.7352055276539985</v>
       </c>
       <c r="G63">
-        <v>-3.545019388303942</v>
+        <v>-5.225733700408835</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.906274208654823</v>
       </c>
       <c r="E64">
-        <v>-6.713039116522186</v>
+        <v>-9.563876529414951</v>
       </c>
       <c r="F64">
-        <v>2.043210415098254</v>
+        <v>0.4334145284078574</v>
       </c>
       <c r="G64">
-        <v>-3.173208708242856</v>
+        <v>-4.89361315081807</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.12417342628723</v>
       </c>
       <c r="E65">
-        <v>-6.562009979892371</v>
+        <v>-10.25801461073269</v>
       </c>
       <c r="F65">
-        <v>2.321260078966043</v>
+        <v>0.6445114409945276</v>
       </c>
       <c r="G65">
-        <v>-4.09820161627954</v>
+        <v>-5.278861335223058</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.33312522466222</v>
       </c>
       <c r="E66">
-        <v>-6.707414751804659</v>
+        <v>-8.823086108870196</v>
       </c>
       <c r="F66">
-        <v>1.966338913668739</v>
+        <v>0.4001646227132062</v>
       </c>
       <c r="G66">
-        <v>-4.067595622768978</v>
+        <v>-4.705166967086137</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.53227810173593</v>
       </c>
       <c r="E67">
-        <v>-7.438976142321782</v>
+        <v>-9.271472962739677</v>
       </c>
       <c r="F67">
-        <v>2.072231825998682</v>
+        <v>0.4240239441822591</v>
       </c>
       <c r="G67">
-        <v>-4.248275266665781</v>
+        <v>-5.60926702222448</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.71743959017472</v>
       </c>
       <c r="E68">
-        <v>-5.742188630965753</v>
+        <v>-10.03769529331151</v>
       </c>
       <c r="F68">
-        <v>1.899421003917761</v>
+        <v>0.06260166610207654</v>
       </c>
       <c r="G68">
-        <v>-4.292835209624371</v>
+        <v>-5.1196903056949</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.88732016468899</v>
       </c>
       <c r="E69">
-        <v>-6.97305956556861</v>
+        <v>-9.321689211010733</v>
       </c>
       <c r="F69">
-        <v>1.641639608355766</v>
+        <v>0.1699808864336597</v>
       </c>
       <c r="G69">
-        <v>-4.352358818420467</v>
+        <v>-5.944022766064504</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.03299814567017</v>
       </c>
       <c r="E70">
-        <v>-5.923707983089212</v>
+        <v>-8.809536914639247</v>
       </c>
       <c r="F70">
-        <v>1.642556574080806</v>
+        <v>-0.1306231252288595</v>
       </c>
       <c r="G70">
-        <v>-4.872611049916935</v>
+        <v>-5.713304226341616</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.1512140940411</v>
       </c>
       <c r="E71">
-        <v>-5.82729677146591</v>
+        <v>-7.765116840354201</v>
       </c>
       <c r="F71">
-        <v>1.615581311223125</v>
+        <v>-0.1061018146871529</v>
       </c>
       <c r="G71">
-        <v>-4.388831098626618</v>
+        <v>-4.973367503404653</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.23487843528553</v>
       </c>
       <c r="E72">
-        <v>-7.148682844534082</v>
+        <v>-8.531370870244087</v>
       </c>
       <c r="F72">
-        <v>1.16861199070865</v>
+        <v>-0.3345680219014053</v>
       </c>
       <c r="G72">
-        <v>-4.569292246517829</v>
+        <v>-5.814696304572875</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.27634292945848</v>
       </c>
       <c r="E73">
-        <v>-6.88667439539829</v>
+        <v>-8.853100834593036</v>
       </c>
       <c r="F73">
-        <v>1.195992682280683</v>
+        <v>-0.1629069703150927</v>
       </c>
       <c r="G73">
-        <v>-3.826813024606706</v>
+        <v>-5.404950083177281</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.27433871694099</v>
       </c>
       <c r="E74">
-        <v>-5.677630705512405</v>
+        <v>-8.784476339480799</v>
       </c>
       <c r="F74">
-        <v>1.156458631513568</v>
+        <v>0.04541053838998135</v>
       </c>
       <c r="G74">
-        <v>-4.267029507145752</v>
+        <v>-4.728221606221622</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.22523627965946</v>
       </c>
       <c r="E75">
-        <v>-6.235153782966741</v>
+        <v>-9.338150214028616</v>
       </c>
       <c r="F75">
-        <v>1.021306752395881</v>
+        <v>-0.05004258454538503</v>
       </c>
       <c r="G75">
-        <v>-4.257723563634861</v>
+        <v>-4.830126819011467</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.13274962842045</v>
       </c>
       <c r="E76">
-        <v>-6.488141511879252</v>
+        <v>-9.815265707002757</v>
       </c>
       <c r="F76">
-        <v>0.5634177795944507</v>
+        <v>-0.7754867939659441</v>
       </c>
       <c r="G76">
-        <v>-4.020771266661526</v>
+        <v>-5.447209196986077</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.00041164335432</v>
       </c>
       <c r="E77">
-        <v>-7.238251531931794</v>
+        <v>-11.38275170001777</v>
       </c>
       <c r="F77">
-        <v>1.006195030550758</v>
+        <v>-0.4993811291093577</v>
       </c>
       <c r="G77">
-        <v>-4.090031189888618</v>
+        <v>-5.033629363856006</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.83221230327517</v>
       </c>
       <c r="E78">
-        <v>-8.151273404410276</v>
+        <v>-10.6940206166652</v>
       </c>
       <c r="F78">
-        <v>0.956664628045389</v>
+        <v>-0.9408557819502158</v>
       </c>
       <c r="G78">
-        <v>-4.453019266087547</v>
+        <v>-5.214620199033502</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.63782752327708</v>
       </c>
       <c r="E79">
-        <v>-7.515942086556148</v>
+        <v>-10.54773732079542</v>
       </c>
       <c r="F79">
-        <v>0.6252915860047545</v>
+        <v>-0.7293383954429964</v>
       </c>
       <c r="G79">
-        <v>-3.765733459407152</v>
+        <v>-4.241164214847426</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.42122515267617</v>
       </c>
       <c r="E80">
-        <v>-9.104014522410035</v>
+        <v>-12.32355123205931</v>
       </c>
       <c r="F80">
-        <v>0.4145082471893413</v>
+        <v>-0.4437384136233504</v>
       </c>
       <c r="G80">
-        <v>-3.812703479518332</v>
+        <v>-4.126668997371732</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.19203036089695</v>
       </c>
       <c r="E81">
-        <v>-10.44697877412476</v>
+        <v>-12.72157239801548</v>
       </c>
       <c r="F81">
-        <v>0.6433252452638635</v>
+        <v>-1.044960690301628</v>
       </c>
       <c r="G81">
-        <v>-3.382451739052491</v>
+        <v>-3.688594437796594</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.955082352518044</v>
       </c>
       <c r="E82">
-        <v>-11.04933827272904</v>
+        <v>-11.47967915767795</v>
       </c>
       <c r="F82">
-        <v>0.3622934631573027</v>
+        <v>-0.961078122784462</v>
       </c>
       <c r="G82">
-        <v>-3.284883340919091</v>
+        <v>-4.243683540002812</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.717293909979645</v>
       </c>
       <c r="E83">
-        <v>-12.52785786538936</v>
+        <v>-15.12336179983364</v>
       </c>
       <c r="F83">
-        <v>0.2590770138244521</v>
+        <v>-0.7739806896403612</v>
       </c>
       <c r="G83">
-        <v>-2.708176376341432</v>
+        <v>-4.28593603272053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.486537667147962</v>
       </c>
       <c r="E84">
-        <v>-12.37281650078875</v>
+        <v>-13.80956092072832</v>
       </c>
       <c r="F84">
-        <v>0.1027620725587478</v>
+        <v>-1.060028860234076</v>
       </c>
       <c r="G84">
-        <v>-1.969500971254931</v>
+        <v>-3.783358803858232</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.264453084842287</v>
       </c>
       <c r="E85">
-        <v>-13.11226196455323</v>
+        <v>-15.51549594957984</v>
       </c>
       <c r="F85">
-        <v>0.1713088238437556</v>
+        <v>-1.077442498627291</v>
       </c>
       <c r="G85">
-        <v>-2.138861859952966</v>
+        <v>-3.809422728888914</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.058789588092139</v>
       </c>
       <c r="E86">
-        <v>-14.51640137163757</v>
+        <v>-15.14601322682001</v>
       </c>
       <c r="F86">
-        <v>0.165507709075501</v>
+        <v>-1.246636928250306</v>
       </c>
       <c r="G86">
-        <v>-1.894017222414008</v>
+        <v>-3.478262237504539</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.870059503087164</v>
       </c>
       <c r="E87">
-        <v>-15.26865788836975</v>
+        <v>-19.10148583287781</v>
       </c>
       <c r="F87">
-        <v>-0.1261087715168994</v>
+        <v>-1.002675742359395</v>
       </c>
       <c r="G87">
-        <v>-1.753527601363957</v>
+        <v>-2.926387675016953</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.701285015233609</v>
       </c>
       <c r="E88">
-        <v>-18.34316568944937</v>
+        <v>-19.95237251349705</v>
       </c>
       <c r="F88">
-        <v>-0.2705364161813152</v>
+        <v>-1.289531602969984</v>
       </c>
       <c r="G88">
-        <v>-2.428501489183802</v>
+        <v>-4.022168316879098</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.554726030649467</v>
       </c>
       <c r="E89">
-        <v>-19.03792417170615</v>
+        <v>-20.34171712325453</v>
       </c>
       <c r="F89">
-        <v>0.125171511262216</v>
+        <v>-1.033362420029907</v>
       </c>
       <c r="G89">
-        <v>-1.453665007507851</v>
+        <v>-3.737011166308435</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.429451918189358</v>
       </c>
       <c r="E90">
-        <v>-19.4764298952909</v>
+        <v>-21.55403037137395</v>
       </c>
       <c r="F90">
-        <v>0.04766019264286308</v>
+        <v>-1.274856983957522</v>
       </c>
       <c r="G90">
-        <v>-1.638482833328744</v>
+        <v>-2.571907700853952</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.330470026993458</v>
       </c>
       <c r="E91">
-        <v>-22.31307507064362</v>
+        <v>-24.47304396045219</v>
       </c>
       <c r="F91">
-        <v>-0.1885337075857761</v>
+        <v>-1.503354865290083</v>
       </c>
       <c r="G91">
-        <v>-1.44531250111227</v>
+        <v>-3.389340984319714</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.254251108206386</v>
       </c>
       <c r="E92">
-        <v>-25.01031570214423</v>
+        <v>-26.95937091504555</v>
       </c>
       <c r="F92">
-        <v>-0.6607670967162992</v>
+        <v>-1.702919231400523</v>
       </c>
       <c r="G92">
-        <v>-1.628256558157935</v>
+        <v>-2.460683302371057</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.19998659312019</v>
       </c>
       <c r="E93">
-        <v>-26.78113470657765</v>
+        <v>-27.4400367316417</v>
       </c>
       <c r="F93">
-        <v>-0.3311068326232124</v>
+        <v>-1.831943752331375</v>
       </c>
       <c r="G93">
-        <v>-1.458743384365093</v>
+        <v>-2.917426028242146</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.159800062204118</v>
       </c>
       <c r="E94">
-        <v>-27.75818467305059</v>
+        <v>-30.65730241157613</v>
       </c>
       <c r="F94">
-        <v>-0.9559936349429438</v>
+        <v>-1.969437932497997</v>
       </c>
       <c r="G94">
-        <v>-1.377750887746824</v>
+        <v>-2.413047862606484</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.1265544115399</v>
       </c>
       <c r="E95">
-        <v>-30.64833603304094</v>
+        <v>-32.2107705133004</v>
       </c>
       <c r="F95">
-        <v>-0.2430369466656247</v>
+        <v>-2.036663873049529</v>
       </c>
       <c r="G95">
-        <v>-1.245822337461328</v>
+        <v>-2.873024991469441</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.092563335023701</v>
       </c>
       <c r="E96">
-        <v>-33.26513285226929</v>
+        <v>-34.62274898163582</v>
       </c>
       <c r="F96">
-        <v>-0.4736015642178344</v>
+        <v>-1.832130629629397</v>
       </c>
       <c r="G96">
-        <v>-1.423115293271457</v>
+        <v>-3.189235059198468</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.048686947033822</v>
       </c>
       <c r="E97">
-        <v>-35.57511876476696</v>
+        <v>-37.41855864262438</v>
       </c>
       <c r="F97">
-        <v>-1.044821324181069</v>
+        <v>-1.515048949769688</v>
       </c>
       <c r="G97">
-        <v>-2.017825004491672</v>
+        <v>-4.303475302987589</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.990565278050058</v>
       </c>
       <c r="E98">
-        <v>-38.16277258951894</v>
+        <v>-38.86479021561002</v>
       </c>
       <c r="F98">
-        <v>-0.6955357763838568</v>
+        <v>-1.612689170574276</v>
       </c>
       <c r="G98">
-        <v>-1.768540925384552</v>
+        <v>-2.526761791334911</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.915855385347688</v>
       </c>
       <c r="E99">
-        <v>-40.92236577963116</v>
+        <v>-42.31979398823613</v>
       </c>
       <c r="F99">
-        <v>-0.8259618770498725</v>
+        <v>-2.04933510407896</v>
       </c>
       <c r="G99">
-        <v>-2.083238073802132</v>
+        <v>-3.387986971194152</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.821271088540277</v>
       </c>
       <c r="E100">
-        <v>-43.07600839125101</v>
+        <v>-44.9002339538939</v>
       </c>
       <c r="F100">
-        <v>-0.7445910671145937</v>
+        <v>-1.837725070775687</v>
       </c>
       <c r="G100">
-        <v>-2.015716186983156</v>
+        <v>-3.552332383400192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.713842872845555</v>
       </c>
       <c r="E101">
-        <v>-46.23389671999686</v>
+        <v>-46.17860858083721</v>
       </c>
       <c r="F101">
-        <v>-0.7860722843047414</v>
+        <v>-2.212082266920221</v>
       </c>
       <c r="G101">
-        <v>-2.835665485058766</v>
+        <v>-3.79726640566871</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.580804891511827</v>
       </c>
       <c r="E102">
-        <v>-47.84564854643686</v>
+        <v>-49.22391678151538</v>
       </c>
       <c r="F102">
-        <v>-0.6575181240307751</v>
+        <v>-2.401757973294658</v>
       </c>
       <c r="G102">
-        <v>-2.954785534652821</v>
+        <v>-4.038211220562406</v>
       </c>
     </row>
   </sheetData>
